--- a/12517276.xlsx
+++ b/12517276.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1540e1892e12f7ad/Desktop/cap 776 repo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="393" documentId="8_{0F65E909-EBA2-4DDC-9ABF-9793501E95B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B7B8A3A-65AF-489F-9329-F979D0F4B746}"/>
+  <xr:revisionPtr revIDLastSave="666" documentId="8_{0F65E909-EBA2-4DDC-9ABF-9793501E95B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FC89F4D-0150-49E6-95E2-0107E1E46F7C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -235,6 +235,15 @@
   </si>
   <si>
     <t>High</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not tired </t>
   </si>
 </sst>
 </file>
@@ -1721,7 +1730,7 @@
         <v>120</v>
       </c>
       <c r="E21" s="14">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="F21" s="14">
         <v>0</v>
@@ -1734,11 +1743,11 @@
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>1015</v>
+        <v>1185</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>425</v>
+        <v>255</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>63</v>
@@ -1746,7 +1755,9 @@
       <c r="L21" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M21" s="16"/>
+      <c r="M21" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="N21" s="17" t="s">
         <v>62</v>
       </c>
@@ -1790,7 +1801,9 @@
       <c r="L22" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M22" s="16"/>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N22" s="17" t="s">
         <v>62</v>
       </c>
@@ -1834,7 +1847,9 @@
       <c r="L23" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M23" s="16"/>
+      <c r="M23" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N23" s="17" t="s">
         <v>62</v>
       </c>
@@ -1878,7 +1893,9 @@
       <c r="L24" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M24" s="16"/>
+      <c r="M24" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N24" s="17" t="s">
         <v>62</v>
       </c>
@@ -1922,7 +1939,9 @@
       <c r="L25" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M25" s="16"/>
+      <c r="M25" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N25" s="17" t="s">
         <v>62</v>
       </c>
@@ -1966,7 +1985,9 @@
       <c r="L26" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M26" s="16"/>
+      <c r="M26" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N26" s="17" t="s">
         <v>62</v>
       </c>
@@ -2010,7 +2031,9 @@
       <c r="L27" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M27" s="16"/>
+      <c r="M27" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N27" s="17" t="s">
         <v>62</v>
       </c>
@@ -2054,7 +2077,9 @@
       <c r="L28" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M28" s="16"/>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N28" s="17" t="s">
         <v>62</v>
       </c>
@@ -2098,7 +2123,9 @@
       <c r="L29" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M29" s="16"/>
+      <c r="M29" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="N29" s="17" t="s">
         <v>62</v>
       </c>
@@ -2120,21 +2147,21 @@
         <v>30</v>
       </c>
       <c r="F30" s="14">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G30" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H30" s="14">
         <v>400</v>
       </c>
       <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v>1335</v>
+        <v>1385</v>
       </c>
       <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="K30" s="16" t="s">
         <v>59</v>
@@ -2142,7 +2169,9 @@
       <c r="L30" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M30" s="16"/>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N30" s="17" t="s">
         <v>62</v>
       </c>
@@ -2186,7 +2215,9 @@
       <c r="L31" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M31" s="16"/>
+      <c r="M31" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N31" s="17" t="s">
         <v>62</v>
       </c>
@@ -2230,7 +2261,9 @@
       <c r="L32" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M32" s="16"/>
+      <c r="M32" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N32" s="17" t="s">
         <v>62</v>
       </c>
@@ -2274,7 +2307,9 @@
       <c r="L33" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M33" s="16"/>
+      <c r="M33" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N33" s="17" t="s">
         <v>62</v>
       </c>
@@ -2318,7 +2353,9 @@
       <c r="L34" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M34" s="16"/>
+      <c r="M34" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N34" s="17" t="s">
         <v>62</v>
       </c>
@@ -2334,7 +2371,7 @@
         <v>75</v>
       </c>
       <c r="D35" s="14">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E35" s="14">
         <v>60</v>
@@ -2350,11 +2387,11 @@
       </c>
       <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v>1355</v>
+        <v>1255</v>
       </c>
       <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v>85</v>
+        <v>185</v>
       </c>
       <c r="K35" s="16" t="s">
         <v>59</v>
@@ -2362,7 +2399,9 @@
       <c r="L35" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M35" s="16"/>
+      <c r="M35" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N35" s="17" t="s">
         <v>62</v>
       </c>
@@ -2406,7 +2445,9 @@
       <c r="L36" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M36" s="16"/>
+      <c r="M36" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="N36" s="17" t="s">
         <v>62</v>
       </c>
@@ -2428,21 +2469,21 @@
         <v>120</v>
       </c>
       <c r="F37" s="14">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="G37" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H37" s="14">
         <v>300</v>
       </c>
       <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v>1355</v>
+        <v>1405</v>
       </c>
       <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="K37" s="16" t="s">
         <v>59</v>
@@ -2450,7 +2491,9 @@
       <c r="L37" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M37" s="16"/>
+      <c r="M37" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N37" s="17" t="s">
         <v>62</v>
       </c>
@@ -2459,352 +2502,724 @@
       <c r="A38" s="13">
         <v>46266</v>
       </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="B38" s="14">
+        <v>350</v>
+      </c>
+      <c r="C38" s="14">
+        <v>45</v>
+      </c>
+      <c r="D38" s="14">
+        <v>300</v>
+      </c>
+      <c r="E38" s="14">
+        <v>30</v>
+      </c>
+      <c r="F38" s="14">
+        <v>250</v>
+      </c>
+      <c r="G38" s="14">
+        <v>5</v>
+      </c>
+      <c r="H38" s="14">
+        <v>300</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>1275</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
+        <v>165</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N38" s="17" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B39" s="14">
+        <v>450</v>
+      </c>
+      <c r="C39" s="14">
+        <v>45</v>
+      </c>
+      <c r="D39" s="14">
+        <v>200</v>
+      </c>
+      <c r="E39" s="14">
+        <v>45</v>
+      </c>
+      <c r="F39" s="14">
+        <v>200</v>
+      </c>
+      <c r="G39" s="14">
+        <v>4</v>
+      </c>
+      <c r="H39" s="14">
+        <v>200</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B40" s="14">
+        <v>380</v>
+      </c>
+      <c r="C40" s="14">
+        <v>45</v>
+      </c>
+      <c r="D40" s="14">
+        <v>120</v>
+      </c>
+      <c r="E40" s="14">
+        <v>30</v>
+      </c>
+      <c r="F40" s="14">
+        <v>300</v>
+      </c>
+      <c r="G40" s="14">
+        <v>6</v>
+      </c>
+      <c r="H40" s="14">
+        <v>300</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1175</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>265</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B41" s="14">
+        <v>660</v>
+      </c>
+      <c r="C41" s="14">
+        <v>45</v>
+      </c>
+      <c r="D41" s="14">
+        <v>200</v>
+      </c>
+      <c r="E41" s="14">
+        <v>90</v>
+      </c>
+      <c r="F41" s="14">
+        <v>0</v>
+      </c>
+      <c r="G41" s="14">
+        <v>0</v>
+      </c>
+      <c r="H41" s="14">
+        <v>300</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1295</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>145</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B42" s="14">
+        <v>660</v>
+      </c>
+      <c r="C42" s="14">
+        <v>40</v>
+      </c>
+      <c r="D42" s="14">
+        <v>300</v>
+      </c>
+      <c r="E42" s="14">
+        <v>90</v>
+      </c>
+      <c r="F42" s="14">
+        <v>150</v>
+      </c>
+      <c r="G42" s="14">
+        <v>3</v>
+      </c>
+      <c r="H42" s="14">
+        <v>200</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B43" s="14">
+        <v>660</v>
+      </c>
+      <c r="C43" s="14">
+        <v>45</v>
+      </c>
+      <c r="D43" s="14">
+        <v>300</v>
+      </c>
+      <c r="E43" s="14">
+        <v>90</v>
+      </c>
+      <c r="F43" s="14">
+        <v>0</v>
+      </c>
+      <c r="G43" s="14">
+        <v>0</v>
+      </c>
+      <c r="H43" s="14">
+        <v>200</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1295</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>145</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B44" s="14">
+        <v>450</v>
+      </c>
+      <c r="C44" s="14">
+        <v>45</v>
+      </c>
+      <c r="D44" s="14">
+        <v>100</v>
+      </c>
+      <c r="E44" s="14">
+        <v>45</v>
+      </c>
+      <c r="F44" s="14">
+        <v>350</v>
+      </c>
+      <c r="G44" s="14">
+        <v>7</v>
+      </c>
+      <c r="H44" s="14">
+        <v>100</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>350</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B45" s="14">
+        <v>300</v>
+      </c>
+      <c r="C45" s="14">
+        <v>45</v>
+      </c>
+      <c r="D45" s="14">
+        <v>200</v>
+      </c>
+      <c r="E45" s="14">
+        <v>45</v>
+      </c>
+      <c r="F45" s="14">
+        <v>250</v>
+      </c>
+      <c r="G45" s="14">
+        <v>5</v>
+      </c>
+      <c r="H45" s="14">
+        <v>100</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B46" s="14">
+        <v>360</v>
+      </c>
+      <c r="C46" s="14">
+        <v>45</v>
+      </c>
+      <c r="D46" s="14">
+        <v>120</v>
+      </c>
+      <c r="E46" s="14">
+        <v>30</v>
+      </c>
+      <c r="F46" s="14">
+        <v>200</v>
+      </c>
+      <c r="G46" s="14">
+        <v>4</v>
+      </c>
+      <c r="H46" s="14">
+        <v>300</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1055</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>385</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B47" s="14">
+        <v>420</v>
+      </c>
+      <c r="C47" s="14">
+        <v>45</v>
+      </c>
+      <c r="D47" s="14">
+        <v>100</v>
+      </c>
+      <c r="E47" s="14">
+        <v>90</v>
+      </c>
+      <c r="F47" s="14">
+        <v>300</v>
+      </c>
+      <c r="G47" s="14">
+        <v>6</v>
+      </c>
+      <c r="H47" s="14">
+        <v>200</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>1155</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>285</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B48" s="14">
+        <v>660</v>
+      </c>
+      <c r="C48" s="14">
+        <v>45</v>
+      </c>
+      <c r="D48" s="14">
+        <v>200</v>
+      </c>
+      <c r="E48" s="14">
+        <v>120</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0</v>
+      </c>
+      <c r="G48" s="14">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14">
+        <v>400</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>1425</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+        <v>15</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B49" s="14">
+        <v>660</v>
+      </c>
+      <c r="C49" s="14">
+        <v>45</v>
+      </c>
+      <c r="D49" s="14">
+        <v>390</v>
+      </c>
+      <c r="E49" s="14">
+        <v>100</v>
+      </c>
+      <c r="F49" s="14">
+        <v>0</v>
+      </c>
+      <c r="G49" s="14">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14">
+        <v>200</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>1395</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+        <v>45</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B50" s="14">
+        <v>660</v>
+      </c>
+      <c r="C50" s="14">
+        <v>45</v>
+      </c>
+      <c r="D50" s="14">
+        <v>200</v>
+      </c>
+      <c r="E50" s="14">
+        <v>100</v>
+      </c>
+      <c r="F50" s="14">
+        <v>0</v>
+      </c>
+      <c r="G50" s="14">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14">
+        <v>300</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>1305</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+        <v>135</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B51" s="14">
+        <v>500</v>
+      </c>
+      <c r="C51" s="14">
+        <v>45</v>
+      </c>
+      <c r="D51" s="14">
+        <v>200</v>
+      </c>
+      <c r="E51" s="14">
+        <v>45</v>
+      </c>
+      <c r="F51" s="14">
+        <v>350</v>
+      </c>
+      <c r="G51" s="14">
+        <v>7</v>
+      </c>
+      <c r="H51" s="14">
+        <v>200</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+        <v>100</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B52" s="14">
+        <v>300</v>
+      </c>
+      <c r="C52" s="14">
+        <v>45</v>
+      </c>
+      <c r="D52" s="14">
+        <v>100</v>
+      </c>
+      <c r="E52" s="14">
+        <v>50</v>
+      </c>
+      <c r="F52" s="14">
+        <v>250</v>
+      </c>
+      <c r="G52" s="14">
+        <v>5</v>
+      </c>
+      <c r="H52" s="14">
+        <v>200</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>945</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+        <v>495</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B53" s="14">
+        <v>350</v>
+      </c>
+      <c r="C53" s="14">
+        <v>45</v>
+      </c>
+      <c r="D53" s="14">
+        <v>300</v>
+      </c>
+      <c r="E53" s="14">
+        <v>100</v>
+      </c>
+      <c r="F53" s="14">
+        <v>100</v>
+      </c>
+      <c r="G53" s="14">
+        <v>2</v>
+      </c>
+      <c r="H53" s="14">
+        <v>400</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>1295</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>145</v>
       </c>
       <c r="K53" s="16"/>
       <c r="L53" s="16"/>
@@ -2812,21 +3227,37 @@
       <c r="N53" s="17"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B54" s="14">
+        <v>360</v>
+      </c>
+      <c r="C54" s="14">
+        <v>45</v>
+      </c>
+      <c r="D54" s="14">
+        <v>200</v>
+      </c>
+      <c r="E54" s="14">
+        <v>120</v>
+      </c>
+      <c r="F54" s="14">
+        <v>300</v>
+      </c>
+      <c r="G54" s="14">
+        <v>6</v>
+      </c>
+      <c r="H54" s="14">
+        <v>150</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>1175</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>265</v>
       </c>
       <c r="K54" s="16"/>
       <c r="L54" s="16"/>
@@ -2834,21 +3265,37 @@
       <c r="N54" s="17"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B55" s="14">
+        <v>660</v>
+      </c>
+      <c r="C55" s="14">
+        <v>45</v>
+      </c>
+      <c r="D55" s="14">
+        <v>400</v>
+      </c>
+      <c r="E55" s="14">
+        <v>45</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>120</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>170</v>
       </c>
       <c r="K55" s="16"/>
       <c r="L55" s="16"/>
@@ -2856,21 +3303,37 @@
       <c r="N55" s="17"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B56" s="14">
+        <v>650</v>
+      </c>
+      <c r="C56" s="14">
+        <v>45</v>
+      </c>
+      <c r="D56" s="14">
+        <v>300</v>
+      </c>
+      <c r="E56" s="14">
+        <v>90</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>200</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>1285</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>155</v>
       </c>
       <c r="K56" s="16"/>
       <c r="L56" s="16"/>
@@ -2878,21 +3341,37 @@
       <c r="N56" s="17"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="A57" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B57" s="14">
+        <v>670</v>
+      </c>
+      <c r="C57" s="14">
+        <v>45</v>
+      </c>
+      <c r="D57" s="14">
+        <v>300</v>
+      </c>
+      <c r="E57" s="14">
+        <v>60</v>
+      </c>
+      <c r="F57" s="14">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <v>0</v>
+      </c>
+      <c r="H57" s="14">
+        <v>300</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>1375</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>65</v>
       </c>
       <c r="K57" s="16"/>
       <c r="L57" s="16"/>
@@ -2900,21 +3379,37 @@
       <c r="N57" s="17"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+      <c r="A58" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B58" s="14">
+        <v>360</v>
+      </c>
+      <c r="C58" s="14">
+        <v>45</v>
+      </c>
+      <c r="D58" s="14">
+        <v>120</v>
+      </c>
+      <c r="E58" s="14">
+        <v>45</v>
+      </c>
+      <c r="F58" s="14">
+        <v>350</v>
+      </c>
+      <c r="G58" s="14">
+        <v>7</v>
+      </c>
+      <c r="H58" s="14">
+        <v>220</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>300</v>
       </c>
       <c r="K58" s="16"/>
       <c r="L58" s="16"/>

--- a/12517276.xlsx
+++ b/12517276.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1540e1892e12f7ad/Desktop/cap 776 repo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="666" documentId="8_{0F65E909-EBA2-4DDC-9ABF-9793501E95B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FC89F4D-0150-49E6-95E2-0107E1E46F7C}"/>
+  <xr:revisionPtr revIDLastSave="691" documentId="8_{0F65E909-EBA2-4DDC-9ABF-9793501E95B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98009067-CE43-4131-B3AD-2611A7EF15B9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -244,6 +244,9 @@
   </si>
   <si>
     <t xml:space="preserve">not tired </t>
+  </si>
+  <si>
+    <t>Excellent</t>
   </si>
 </sst>
 </file>
@@ -3221,10 +3224,18 @@
         <f t="shared" si="1"/>
         <v>145</v>
       </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
+      <c r="K53" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" s="13">
@@ -3259,10 +3270,18 @@
         <f t="shared" si="1"/>
         <v>265</v>
       </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
+      <c r="K54" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" s="13">
@@ -3297,10 +3316,18 @@
         <f t="shared" si="1"/>
         <v>170</v>
       </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+      <c r="K55" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" s="13">
@@ -3335,10 +3362,18 @@
         <f t="shared" si="1"/>
         <v>155</v>
       </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+      <c r="K56" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" s="13">
@@ -3373,10 +3408,18 @@
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
+      <c r="K57" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" s="13">
@@ -3411,10 +3454,18 @@
         <f t="shared" si="1"/>
         <v>300</v>
       </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
+      <c r="K58" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" s="13"/>

--- a/12517276.xlsx
+++ b/12517276.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1540e1892e12f7ad/Desktop/cap 776 repo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="691" documentId="8_{0F65E909-EBA2-4DDC-9ABF-9793501E95B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98009067-CE43-4131-B3AD-2611A7EF15B9}"/>
+  <xr:revisionPtr revIDLastSave="704" documentId="8_{0F65E909-EBA2-4DDC-9ABF-9793501E95B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6955D875-91DF-4BB1-9C1D-6D183AECEDAD}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -210,28 +210,16 @@
     <t>d2537</t>
   </si>
   <si>
-    <t xml:space="preserve">bad  </t>
-  </si>
-  <si>
     <t>Unsatisfied</t>
   </si>
   <si>
     <t>Low</t>
   </si>
   <si>
-    <t xml:space="preserve">extremely tired </t>
-  </si>
-  <si>
-    <t xml:space="preserve">satisfied </t>
-  </si>
-  <si>
     <t>tired</t>
   </si>
   <si>
     <t>bad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">terrible </t>
   </si>
   <si>
     <t>High</t>
@@ -1076,556 +1064,196 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="13">
-        <v>46235</v>
-      </c>
-      <c r="B7" s="14">
-        <v>420</v>
-      </c>
-      <c r="C7" s="14">
-        <v>45</v>
-      </c>
-      <c r="D7" s="14">
-        <v>120</v>
-      </c>
-      <c r="E7" s="14">
-        <v>200</v>
-      </c>
-      <c r="F7" s="14">
-        <v>0</v>
-      </c>
-      <c r="G7" s="14">
-        <v>0</v>
-      </c>
-      <c r="H7" s="14">
-        <v>300</v>
-      </c>
-      <c r="I7" s="15">
-        <f t="shared" si="0"/>
-        <v>1085</v>
-      </c>
-      <c r="J7" s="15">
-        <f t="shared" si="1"/>
-        <v>355</v>
-      </c>
-      <c r="K7" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L7" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M7" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>60</v>
-      </c>
+      <c r="A7" s="13"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="17"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="13">
-        <v>46236</v>
-      </c>
-      <c r="B8" s="14">
-        <v>420</v>
-      </c>
-      <c r="C8" s="14">
-        <v>45</v>
-      </c>
-      <c r="D8" s="14">
-        <v>120</v>
-      </c>
-      <c r="E8" s="14">
-        <v>100</v>
-      </c>
-      <c r="F8" s="14">
-        <v>0</v>
-      </c>
-      <c r="G8" s="14">
-        <v>0</v>
-      </c>
-      <c r="H8" s="14">
-        <v>400</v>
-      </c>
-      <c r="I8" s="15">
-        <f t="shared" si="0"/>
-        <v>1085</v>
-      </c>
-      <c r="J8" s="15">
-        <f t="shared" si="1"/>
-        <v>355</v>
-      </c>
-      <c r="K8" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L8" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="M8" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>62</v>
-      </c>
+      <c r="A8" s="13"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="13">
-        <v>46237</v>
-      </c>
-      <c r="B9" s="14">
-        <v>420</v>
-      </c>
-      <c r="C9" s="14">
-        <v>45</v>
-      </c>
-      <c r="D9" s="14">
-        <v>120</v>
-      </c>
-      <c r="E9" s="14">
-        <v>200</v>
-      </c>
-      <c r="F9" s="14">
-        <v>200</v>
-      </c>
-      <c r="G9" s="14">
-        <v>4</v>
-      </c>
-      <c r="H9" s="14">
-        <v>200</v>
-      </c>
-      <c r="I9" s="15">
-        <f t="shared" si="0"/>
-        <v>1185</v>
-      </c>
-      <c r="J9" s="15">
-        <f t="shared" si="1"/>
-        <v>255</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="L9" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M9" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>62</v>
-      </c>
+      <c r="A9" s="13"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="13">
-        <v>46238</v>
-      </c>
-      <c r="B10" s="14">
-        <v>420</v>
-      </c>
-      <c r="C10" s="14">
-        <v>45</v>
-      </c>
-      <c r="D10" s="14">
-        <v>120</v>
-      </c>
-      <c r="E10" s="14">
-        <v>100</v>
-      </c>
-      <c r="F10" s="14">
-        <v>250</v>
-      </c>
-      <c r="G10" s="14">
-        <v>5</v>
-      </c>
-      <c r="H10" s="14">
-        <v>300</v>
-      </c>
-      <c r="I10" s="15">
-        <f t="shared" si="0"/>
-        <v>1235</v>
-      </c>
-      <c r="J10" s="15">
-        <f t="shared" si="1"/>
-        <v>205</v>
-      </c>
-      <c r="K10" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L10" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M10" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N10" s="17" t="s">
-        <v>62</v>
-      </c>
+      <c r="A10" s="13"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="13">
-        <v>46239</v>
-      </c>
-      <c r="B11" s="14">
-        <v>420</v>
-      </c>
-      <c r="C11" s="14">
-        <v>45</v>
-      </c>
-      <c r="D11" s="14">
-        <v>100</v>
-      </c>
-      <c r="E11" s="14">
-        <v>120</v>
-      </c>
-      <c r="F11" s="14">
-        <v>250</v>
-      </c>
-      <c r="G11" s="14">
-        <v>5</v>
-      </c>
-      <c r="H11" s="14">
-        <v>400</v>
-      </c>
-      <c r="I11" s="15">
-        <f t="shared" si="0"/>
-        <v>1335</v>
-      </c>
-      <c r="J11" s="15">
-        <f t="shared" si="1"/>
-        <v>105</v>
-      </c>
-      <c r="K11" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="L11" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M11" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N11" s="17" t="s">
-        <v>62</v>
-      </c>
+      <c r="A11" s="13"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="13">
-        <v>46240</v>
-      </c>
-      <c r="B12" s="14">
-        <v>420</v>
-      </c>
-      <c r="C12" s="14">
-        <v>35</v>
-      </c>
-      <c r="D12" s="14">
-        <v>60</v>
-      </c>
-      <c r="E12" s="14">
-        <v>100</v>
-      </c>
-      <c r="F12" s="14">
-        <v>300</v>
-      </c>
-      <c r="G12" s="14">
-        <v>6</v>
-      </c>
-      <c r="H12" s="14">
-        <v>400</v>
-      </c>
-      <c r="I12" s="15">
-        <f t="shared" si="0"/>
-        <v>1315</v>
-      </c>
-      <c r="J12" s="15">
-        <f t="shared" si="1"/>
-        <v>125</v>
-      </c>
-      <c r="K12" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="L12" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M12" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N12" s="17" t="s">
-        <v>62</v>
-      </c>
+      <c r="A12" s="13"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="17"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="13">
-        <v>46241</v>
-      </c>
-      <c r="B13" s="14">
-        <v>420</v>
-      </c>
-      <c r="C13" s="14">
-        <v>65</v>
-      </c>
-      <c r="D13" s="14">
-        <v>250</v>
-      </c>
-      <c r="E13" s="14">
-        <v>120</v>
-      </c>
-      <c r="F13" s="14">
-        <v>0</v>
-      </c>
-      <c r="G13" s="14">
-        <v>0</v>
-      </c>
-      <c r="H13" s="14">
-        <v>500</v>
-      </c>
-      <c r="I13" s="15">
-        <f t="shared" si="0"/>
-        <v>1355</v>
-      </c>
-      <c r="J13" s="15">
-        <f t="shared" si="1"/>
-        <v>85</v>
-      </c>
-      <c r="K13" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="L13" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M13" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N13" s="17" t="s">
-        <v>62</v>
-      </c>
+      <c r="A13" s="13"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="13">
-        <v>46242</v>
-      </c>
-      <c r="B14" s="14">
-        <v>420</v>
-      </c>
-      <c r="C14" s="14">
-        <v>55</v>
-      </c>
-      <c r="D14" s="14">
-        <v>300</v>
-      </c>
-      <c r="E14" s="14">
-        <v>200</v>
-      </c>
-      <c r="F14" s="14">
-        <v>0</v>
-      </c>
-      <c r="G14" s="14">
-        <v>0</v>
-      </c>
-      <c r="H14" s="14">
-        <v>300</v>
-      </c>
-      <c r="I14" s="15">
-        <f t="shared" si="0"/>
-        <v>1275</v>
-      </c>
-      <c r="J14" s="15">
-        <f t="shared" si="1"/>
-        <v>165</v>
-      </c>
-      <c r="K14" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="L14" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M14" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N14" s="17" t="s">
-        <v>62</v>
-      </c>
+      <c r="A14" s="13"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="13">
-        <v>46243</v>
-      </c>
-      <c r="B15" s="14">
-        <v>420</v>
-      </c>
-      <c r="C15" s="14">
-        <v>75</v>
-      </c>
-      <c r="D15" s="14">
-        <v>140</v>
-      </c>
-      <c r="E15" s="14">
-        <v>300</v>
-      </c>
-      <c r="F15" s="14">
-        <v>0</v>
-      </c>
-      <c r="G15" s="14">
-        <v>0</v>
-      </c>
-      <c r="H15" s="14">
-        <v>400</v>
-      </c>
-      <c r="I15" s="15">
-        <f t="shared" si="0"/>
-        <v>1335</v>
-      </c>
-      <c r="J15" s="15">
-        <f t="shared" si="1"/>
-        <v>105</v>
-      </c>
-      <c r="K15" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="L15" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M15" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N15" s="17" t="s">
-        <v>62</v>
-      </c>
+      <c r="A15" s="13"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="13">
-        <v>46244</v>
-      </c>
-      <c r="B16" s="14">
-        <v>420</v>
-      </c>
-      <c r="C16" s="14">
-        <v>85</v>
-      </c>
-      <c r="D16" s="14">
-        <v>200</v>
-      </c>
-      <c r="E16" s="14">
-        <v>200</v>
-      </c>
-      <c r="F16" s="14">
-        <v>200</v>
-      </c>
-      <c r="G16" s="14">
-        <v>4</v>
-      </c>
-      <c r="H16" s="14">
-        <v>300</v>
-      </c>
-      <c r="I16" s="15">
-        <f t="shared" si="0"/>
-        <v>1405</v>
-      </c>
-      <c r="J16" s="15">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-      <c r="K16" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="L16" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M16" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>62</v>
-      </c>
+      <c r="A16" s="13"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="13">
-        <v>46245</v>
-      </c>
-      <c r="B17" s="14">
-        <v>420</v>
-      </c>
-      <c r="C17" s="14">
-        <v>25</v>
-      </c>
-      <c r="D17" s="14">
-        <v>300</v>
-      </c>
-      <c r="E17" s="14">
-        <v>100</v>
-      </c>
-      <c r="F17" s="14">
-        <v>250</v>
-      </c>
-      <c r="G17" s="14">
-        <v>5</v>
-      </c>
-      <c r="H17" s="14">
-        <v>300</v>
-      </c>
-      <c r="I17" s="15">
-        <f t="shared" si="0"/>
-        <v>1395</v>
-      </c>
-      <c r="J17" s="15">
-        <f t="shared" si="1"/>
-        <v>45</v>
-      </c>
-      <c r="K17" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="L17" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M17" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N17" s="17" t="s">
-        <v>62</v>
-      </c>
+      <c r="A17" s="13"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="13">
-        <v>46246</v>
-      </c>
-      <c r="B18" s="14">
-        <v>420</v>
-      </c>
-      <c r="C18" s="14">
-        <v>75</v>
-      </c>
-      <c r="D18" s="14">
-        <v>160</v>
-      </c>
-      <c r="E18" s="14">
-        <v>30</v>
-      </c>
-      <c r="F18" s="14">
-        <v>250</v>
-      </c>
-      <c r="G18" s="14">
-        <v>5</v>
-      </c>
-      <c r="H18" s="14">
-        <v>300</v>
-      </c>
-      <c r="I18" s="15">
-        <f t="shared" si="0"/>
-        <v>1235</v>
-      </c>
-      <c r="J18" s="15">
-        <f t="shared" si="1"/>
-        <v>205</v>
-      </c>
-      <c r="K18" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="L18" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M18" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>62</v>
-      </c>
+      <c r="A18" s="13"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="13">
@@ -1661,16 +1289,16 @@
         <v>15</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L19" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M19" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M19" s="16" t="s">
+      <c r="N19" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="N19" s="17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
@@ -1707,16 +1335,16 @@
         <v>255</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M20" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
@@ -1753,16 +1381,16 @@
         <v>255</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
@@ -1799,16 +1427,16 @@
         <v>175</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M22" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
@@ -1845,16 +1473,16 @@
         <v>15</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L23" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M23" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M23" s="16" t="s">
+      <c r="N23" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="N23" s="17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
@@ -1891,16 +1519,16 @@
         <v>95</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L24" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M24" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M24" s="16" t="s">
+      <c r="N24" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="N24" s="17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
@@ -1937,16 +1565,16 @@
         <v>65</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L25" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M25" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M25" s="16" t="s">
+      <c r="N25" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="N25" s="17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
@@ -1983,16 +1611,16 @@
         <v>75</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M26" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M26" s="16" t="s">
+      <c r="N26" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="N26" s="17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
@@ -2029,16 +1657,16 @@
         <v>345</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M27" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
@@ -2075,16 +1703,16 @@
         <v>155</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M28" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
@@ -2121,16 +1749,16 @@
         <v>205</v>
       </c>
       <c r="K29" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N29" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="L29" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M29" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="N29" s="17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
@@ -2167,16 +1795,16 @@
         <v>55</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M30" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
@@ -2213,16 +1841,16 @@
         <v>35</v>
       </c>
       <c r="K31" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N31" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="L31" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M31" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N31" s="17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
@@ -2259,16 +1887,16 @@
         <v>155</v>
       </c>
       <c r="K32" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N32" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="L32" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M32" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N32" s="17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
@@ -2305,16 +1933,16 @@
         <v>175</v>
       </c>
       <c r="K33" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N33" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="L33" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M33" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N33" s="17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
@@ -2351,16 +1979,16 @@
         <v>125</v>
       </c>
       <c r="K34" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N34" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="L34" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M34" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N34" s="17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
@@ -2397,16 +2025,16 @@
         <v>185</v>
       </c>
       <c r="K35" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N35" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="L35" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M35" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N35" s="17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
@@ -2443,16 +2071,16 @@
         <v>295</v>
       </c>
       <c r="K36" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N36" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="L36" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M36" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="N36" s="17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
@@ -2489,16 +2117,16 @@
         <v>35</v>
       </c>
       <c r="K37" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N37" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="L37" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M37" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N37" s="17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
@@ -2535,16 +2163,16 @@
         <v>165</v>
       </c>
       <c r="K38" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L38" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M38" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N38" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="N38" s="17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
@@ -2581,16 +2209,16 @@
         <v>300</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L39" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M39" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M39" s="16" t="s">
+      <c r="N39" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="N39" s="17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
@@ -2627,16 +2255,16 @@
         <v>265</v>
       </c>
       <c r="K40" s="16" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L40" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M40" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
@@ -2673,16 +2301,16 @@
         <v>145</v>
       </c>
       <c r="K41" s="16" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="L41" s="16" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="M41" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N41" s="17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
@@ -2719,16 +2347,16 @@
         <v>0</v>
       </c>
       <c r="K42" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L42" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M42" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N42" s="17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
@@ -2765,16 +2393,16 @@
         <v>145</v>
       </c>
       <c r="K43" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L43" s="16" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="M43" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N43" s="17" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
@@ -2811,16 +2439,16 @@
         <v>350</v>
       </c>
       <c r="K44" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N44" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="L44" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M44" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N44" s="17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
@@ -2857,16 +2485,16 @@
         <v>500</v>
       </c>
       <c r="K45" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L45" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M45" s="16" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="N45" s="17" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
@@ -2903,16 +2531,16 @@
         <v>385</v>
       </c>
       <c r="K46" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L46" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M46" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N46" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="N46" s="17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
@@ -2949,16 +2577,16 @@
         <v>285</v>
       </c>
       <c r="K47" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L47" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M47" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N47" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="N47" s="17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
@@ -2995,16 +2623,16 @@
         <v>15</v>
       </c>
       <c r="K48" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L48" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M48" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N48" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="N48" s="17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
@@ -3041,16 +2669,16 @@
         <v>45</v>
       </c>
       <c r="K49" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L49" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M49" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N49" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="N49" s="17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
@@ -3087,16 +2715,16 @@
         <v>135</v>
       </c>
       <c r="K50" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L50" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M50" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N50" s="17" t="s">
         <v>59</v>
-      </c>
-      <c r="N50" s="17" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
@@ -3133,16 +2761,16 @@
         <v>100</v>
       </c>
       <c r="K51" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L51" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M51" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M51" s="16" t="s">
-        <v>59</v>
-      </c>
       <c r="N51" s="17" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
@@ -3185,10 +2813,10 @@
         <v>50</v>
       </c>
       <c r="M52" s="16" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="N52" s="17" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
@@ -3225,16 +2853,16 @@
         <v>145</v>
       </c>
       <c r="K53" s="16" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="L53" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M53" s="16" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="N53" s="17" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.35">
@@ -3271,16 +2899,16 @@
         <v>265</v>
       </c>
       <c r="K54" s="16" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="L54" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M54" s="16" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="N54" s="17" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.35">
@@ -3317,16 +2945,16 @@
         <v>170</v>
       </c>
       <c r="K55" s="16" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="L55" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M55" s="16" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="N55" s="17" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
@@ -3363,16 +2991,16 @@
         <v>155</v>
       </c>
       <c r="K56" s="16" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="L56" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M56" s="16" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="N56" s="17" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.35">
@@ -3415,10 +3043,10 @@
         <v>50</v>
       </c>
       <c r="M57" s="16" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="N57" s="17" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.35">
@@ -3461,10 +3089,10 @@
         <v>50</v>
       </c>
       <c r="M58" s="16" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="N58" s="17" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.35">

--- a/12517276.xlsx
+++ b/12517276.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1540e1892e12f7ad/Desktop/cap 776 repo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="708" documentId="8_{0F65E909-EBA2-4DDC-9ABF-9793501E95B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71777326-FE9F-4F28-A614-E75BA5965693}"/>
+  <xr:revisionPtr revIDLastSave="714" documentId="8_{0F65E909-EBA2-4DDC-9ABF-9793501E95B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1553E96E-C8DA-46FD-ACC7-F77BF300DE46}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1026,7 +1026,7 @@
         <v>15</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L6" s="11" t="s">
         <v>56</v>
@@ -1072,7 +1072,7 @@
         <v>255</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L7" s="11" t="s">
         <v>56</v>
@@ -1118,7 +1118,7 @@
         <v>255</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="L8" s="11" t="s">
         <v>56</v>
@@ -1164,7 +1164,7 @@
         <v>175</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="L9" s="11" t="s">
         <v>56</v>
@@ -1210,7 +1210,7 @@
         <v>15</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L10" s="11" t="s">
         <v>56</v>
@@ -1256,7 +1256,7 @@
         <v>95</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L11" s="11" t="s">
         <v>56</v>
